--- a/results/Int Task Remove ACC 0.8/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.8/Linea_fi_all.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0032907662082514943 +/- 0.0014578410687284813</t>
+          <t>0.0033398821218074805 +/- 0.001486517283931398</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.001768172888015751 +/- 0.0033108643509533885</t>
+          <t>0.0017681728880157622 +/- 0.0033181425842936283</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.06178781925343809 +/- 0.004704884092270346</t>
+          <t>-0.06183693516699409 +/- 0.004713336676869697</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.013408644400785808 +/- 0.0048425899668791145</t>
+          <t>-0.013359528487229811 +/- 0.0047811762371858324</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.03269230769230769 +/- 0.0030853694611524787</t>
+          <t>0.032638888888888884 +/- 0.00306355789720932</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1801,72 +1801,72 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>0.00021367521367521292 +/- 0.0007629731227075668</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0014423076923076872 +/- 0.0006778086292975146</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.008814102564102533 +/- 0.0016421395458268528</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.008867521367521336 +/- 0.0015519058810185787</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.0011217948717948678 +/- 0.0007722666824145785</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.027670940170940184 +/- 0.002854784020488748</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.036965811965811946 +/- 0.00372248961328724</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.05731837606837609 +/- 0.005733756479372417</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.001388888888888884 +/- 0.0006840944698111994</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.016079059829059848 +/- 0.002696988367812921</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5330128205128205 +/- 0.007897315646400165</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-0.00010683760683760646 +/- 0.0007478632478632452</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.33215811965811964 +/- 0.006747706271212886</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>0.0001602564102564097 +/- 0.0007186764982411144</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.0014423076923076872 +/- 0.0006778086292975146</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.008867521367521336 +/- 0.0015519058810185787</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.008814102564102533 +/- 0.0016421395458268528</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.0011217948717948678 +/- 0.0007722666824145785</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.027670940170940184 +/- 0.002854784020488748</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.036965811965811946 +/- 0.00372248961328724</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.05731837606837609 +/- 0.005733756479372417</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.001388888888888884 +/- 0.0006840944698111994</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.016079059829059848 +/- 0.002696988367812921</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.5330128205128205 +/- 0.007897315646400165</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-0.00010683760683760646 +/- 0.0007478632478632452</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.33215811965811964 +/- 0.006747706271212886</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.00021367521367521292 +/- 0.0007629731227075668</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0020580474934037253 +/- 0.0021815331513028537</t>
+          <t>0.002005277044854914 +/- 0.002160368283953444</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.000493421052631593 +/- 0.000572385225269235</t>
+          <t>-0.0005482456140351033 +/- 0.0006005729797205939</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.000493421052631593 +/- 0.000572385225269235</t>
+          <t>-0.0005482456140351033 +/- 0.0006005729797205939</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.03924820342730789 +/- 0.0024967583837780844</t>
+          <t>0.039192924267551124 +/- 0.002465351367714549</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.04210526315789476 +/- 0.002725731491531423</t>
+          <t>0.04205315268368944 +/- 0.0027480556276050423</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.021111704970603995 +/- 0.004479704600277972</t>
+          <t>0.021058257616248032 +/- 0.004561536781047961</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0021913415285942815 +/- 0.004531692722871497</t>
+          <t>-0.002244788882950244 +/- 0.004527593497498094</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
